--- a/Chapters/Chapter 4 - Compound Fabrcis/Multi Ply.xlsx
+++ b/Chapters/Chapter 4 - Compound Fabrcis/Multi Ply.xlsx
@@ -5,15 +5,15 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Fabric Structure and Design (FSD)\Chapters\Chapter 4 - Double Cloth\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Fabric Structure and Design (FSD)\Chapters\Chapter 4 - Compound Fabrcis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91B8A6A-65F4-49FC-9EE9-7F2F310D21D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03034812-EB4B-4073-AC8F-71D5DE917E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="769" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Extra Thread" sheetId="1" r:id="rId1"/>
+    <sheet name="Multi Ply" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -131,10 +131,10 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
